--- a/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 17,9</t>
+          <t>-8,75; 17,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 17,19</t>
+          <t>-14,88; 17,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 31,57</t>
+          <t>-6,84; 32,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,71; 325,3</t>
+          <t>-56,37; 309,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,06; 436,86</t>
+          <t>-70,22; 306,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 477,69</t>
+          <t>-42,86; 436,29</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 6,59</t>
+          <t>-13,85; 6,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 14,87</t>
+          <t>-11,73; 14,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 8,96</t>
+          <t>-18,1; 7,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,38; 99,52</t>
+          <t>-74,89; 82,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 138,04</t>
+          <t>-53,55; 129,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 72,79</t>
+          <t>-71,21; 56,72</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 12,4</t>
+          <t>-21,04; 13,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 6,05</t>
+          <t>-26,07; 7,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 25,6</t>
+          <t>-3,31; 25,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-76,12; 119,51</t>
+          <t>-76,1; 125,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,23; 44,43</t>
+          <t>-77,18; 50,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 363,22</t>
+          <t>-27,06; 367,81</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -0,88</t>
+          <t>-31,19; -0,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 14,56</t>
+          <t>-26,24; 12,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 15,41</t>
+          <t>-25,74; 17,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,61</t>
+          <t>-98,72; 31,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,04; 121,52</t>
+          <t>-73,38; 126,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,9; 96,37</t>
+          <t>-79,62; 96,82</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 3,51</t>
+          <t>-9,76; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,18</t>
+          <t>-11,55; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 9,54</t>
+          <t>-10,16; 10,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 31,75</t>
+          <t>-52,47; 30,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 26,03</t>
+          <t>-45,9; 24,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 64,24</t>
+          <t>-45,17; 72,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 17,29</t>
+          <t>-9,03; 16,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 17,01</t>
+          <t>-13,1; 17,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 32,15</t>
+          <t>-5,92; 33,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 309,89</t>
+          <t>-60,42; 311,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,22; 306,03</t>
+          <t>-66,15; 410,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 436,29</t>
+          <t>-38,78; 638,14</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 6,08</t>
+          <t>-12,53; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 14,52</t>
+          <t>-12,96; 13,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 7,16</t>
+          <t>-17,03; 8,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,89; 82,09</t>
+          <t>-70,66; 87,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 129,56</t>
+          <t>-56,08; 133,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 56,72</t>
+          <t>-67,93; 80,64</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 13,98</t>
+          <t>-21,95; 13,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 7,05</t>
+          <t>-25,75; 6,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 25,94</t>
+          <t>-3,87; 24,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 125,14</t>
+          <t>-71,88; 140,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 50,32</t>
+          <t>-77,9; 42,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 367,81</t>
+          <t>-23,21; 413,15</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -0,69</t>
+          <t>-31,87; -0,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 12,14</t>
+          <t>-24,94; 14,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 17,19</t>
+          <t>-27,44; 15,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-98,72; 31,78</t>
+          <t>-94,12; 25,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 126,88</t>
+          <t>-76,3; 122,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,62; 96,82</t>
+          <t>-81,87; 98,42</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,44</t>
+          <t>-9,87; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,97</t>
+          <t>-11,43; 4,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,82</t>
+          <t>-11,78; 9,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 30,8</t>
+          <t>-51,33; 29,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 24,54</t>
+          <t>-45,24; 32,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 72,56</t>
+          <t>-49,8; 63,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 16,08</t>
+          <t>-9,07; 17,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 17,94</t>
+          <t>-14,01; 17,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 33,66</t>
+          <t>-9,73; 30,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 311,16</t>
+          <t>-55,71; 325,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 410,29</t>
+          <t>-65,06; 436,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 638,14</t>
+          <t>-54,43; 415,05</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-4,38</t>
+          <t>-1,12</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-23,17%</t>
+          <t>-6,14%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 6,25</t>
+          <t>-12,29; 6,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 13,97</t>
+          <t>-13,61; 14,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 8,71</t>
+          <t>-15,78; 12,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 87,63</t>
+          <t>-74,38; 99,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 133,06</t>
+          <t>-55,46; 138,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 80,64</t>
+          <t>-64,79; 103,17</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 13,84</t>
+          <t>-22,27; 12,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 6,2</t>
+          <t>-27,12; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 24,85</t>
+          <t>-2,86; 26,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 140,77</t>
+          <t>-76,12; 119,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,9; 42,09</t>
+          <t>-77,23; 44,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 413,15</t>
+          <t>-24,1; 373,18</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,41</t>
+          <t>-6,24</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,0%</t>
+          <t>-26,48%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,87; -0,98</t>
+          <t>-32,9; -0,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 14,56</t>
+          <t>-25,82; 14,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 15,51</t>
+          <t>-24,64; 7,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-94,12; 25,05</t>
+          <t>-100,0; 25,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,3; 122,75</t>
+          <t>-76,04; 121,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,87; 98,42</t>
+          <t>-69,21; 55,06</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,15</t>
+          <t>-9,31; 3,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,8</t>
+          <t>-12,21; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 9,51</t>
+          <t>-8,81; 8,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 29,91</t>
+          <t>-50,93; 31,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 32,38</t>
+          <t>-49,56; 26,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 63,97</t>
+          <t>-37,61; 58,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,6 +524,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,43 +542,55 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -582,6 +605,8 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -594,239 +619,185 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7707048396973198</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6127163128578105</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.586363161611319</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="n">
+        <v>0.2602680583483663</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2290784674958303</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3155765439098248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,07; 17,9</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,01; 17,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; 30,08</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-55,71; 325,3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-65,06; 436,86</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-54,43; 415,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-2.556890035785014</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.87720509608083</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.835666527815316</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.6027172478951592</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6775687922164346</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6779612170189</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>4.384449393331989</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.750089489489159</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.263668290998211</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>3.427762704853111</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.399646461024853</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>3.790758540747941</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,87</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-22,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-12,29; 6,59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-13,61; 14,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-15,78; 12,15</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-74,38; 99,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-55,46; 138,04</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-64,79; 103,17</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2675048437801537</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8948964146975928</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7586770649080122</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.01772524894091965</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2844497039126664</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2563416998688159</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.003692270540861394</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-10,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-18,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-39,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.330191964702831</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.516004179017989</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.967049409072816</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.163809508788328</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.7497712784796136</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4948292891070051</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6102890894206756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-22,27; 12,4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-27,12; 6,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 26,06</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-76,12; 119,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-77,23; 44,43</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-24,1; 373,18</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.341694013743476</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.695450624943017</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.522105200681797</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>0.8618753985164004</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2.025809753319939</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.484940216437156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +805,285 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-14,87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,66</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,24</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-67,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-27,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-26,48%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4574260057171359</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3518526953301938</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.561244763970706</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.236307615203708</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1017997718976808</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3454866491234909</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8071454916037886</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-32,9; -0,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-25,82; 14,56</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-24,64; 7,42</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 25,61</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-76,04; 121,52</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-69,21; 55,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.557690127415245</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.870928475932819</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.647678118297899</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.160276122325885</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.7377047646260184</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7795276362274769</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3686679079147579</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.240585881369422</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.49315768457811</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.662653793297976</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>2.375784928912985</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.6693634469587126</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.439941349744727</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3169117786624264</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.901452451854309</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.932476389917529</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.64170454772184</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4893308554735639</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.6355680003690324</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2916557151989752</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3273847632360952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.305801394967903</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.680451370395232</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.713863501408647</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.887016570666427</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.8003405850110336</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7991061885381395</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6845473157227348</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.02577172278088931</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.044740355616643</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.336020505002091</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>0.3679778117395214</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.436266804358282</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.511320525576729</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-20,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-16,33%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-9,31; 3,51</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-12,21; 4,18</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,81; 8,33</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-50,93; 31,75</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-49,56; 26,03</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-37,61; 58,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.2738856552988349</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.671507957350739</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2862626670039708</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.1027005476458086</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.743957402254015</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.213964349385178</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0851358743937965</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.02373919615862251</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7410397768558225</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.981662512349796</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.798007706109021</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.214297346710313</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.518063506707691</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4405694074125874</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4080542466345386</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.09889020852468666</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.688386544041087</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.154712266141316</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.174077010630274</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>0.3343716630701448</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4380421475230336</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.6609020978747435</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -992,14 +1091,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
